--- a/data/trans_bre/P1002-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1002-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,49</t>
+          <t>-0,98; 3,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,8</t>
+          <t>5,15; 11,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,29</t>
+          <t>2,37; 8,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,47</t>
+          <t>1,8; 6,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 120,83</t>
+          <t>-20,93; 114,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,6; 230,1</t>
+          <t>62,68; 230,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,38; 176,67</t>
+          <t>28,06; 180,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,65; 164,28</t>
+          <t>25,57; 169,26</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,34</t>
+          <t>-0,22; 4,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 9,78</t>
+          <t>4,41; 9,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,12</t>
+          <t>4,49; 9,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,95</t>
+          <t>3,68; 8,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 103,54</t>
+          <t>-4,84; 96,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,89; 155,33</t>
+          <t>50,72; 164,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,39; 308,68</t>
+          <t>88,85; 301,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,03; 354,73</t>
+          <t>65,11; 372,4</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 9,03</t>
+          <t>2,82; 9,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 10,15</t>
+          <t>4,21; 10,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 9,12</t>
+          <t>3,58; 9,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 4,3</t>
+          <t>-5,28; 4,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,06; 191,16</t>
+          <t>36,13; 185,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,64; 230,8</t>
+          <t>58,33; 251,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,69; 238,3</t>
+          <t>57,4; 275,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,54; 63,05</t>
+          <t>-55,57; 59,98</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,35</t>
+          <t>1,58; 6,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,43</t>
+          <t>3,69; 9,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,69</t>
+          <t>0,76; 5,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,22</t>
+          <t>3,21; 8,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,85; 144,09</t>
+          <t>23,6; 151,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,93; 159,07</t>
+          <t>41,29; 161,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 102,02</t>
+          <t>9,62; 108,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,0; 193,99</t>
+          <t>50,5; 204,22</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,54</t>
+          <t>2,05; 4,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,68</t>
+          <t>5,79; 8,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,57</t>
+          <t>4,07; 6,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,18</t>
+          <t>2,68; 6,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,16; 97,34</t>
+          <t>35,16; 96,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,5; 140,91</t>
+          <t>79,72; 146,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,92; 137,83</t>
+          <t>69,26; 140,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,94; 135,45</t>
+          <t>45,71; 133,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1002-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1002-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>4,28</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,45%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,45</t>
+          <t>-0,79; 3,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,79</t>
+          <t>5,0; 11,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,49</t>
+          <t>2,16; 8,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,71</t>
+          <t>1,87; 6,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 114,83</t>
+          <t>-18,11; 128,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,68; 230,94</t>
+          <t>64,02; 219,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,06; 180,6</t>
+          <t>28,56; 173,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,57; 169,26</t>
+          <t>24,44; 165,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>139,65%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,15</t>
+          <t>-0,1; 4,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 9,9</t>
+          <t>4,26; 9,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,2</t>
+          <t>4,26; 9,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 8,85</t>
+          <t>2,07; 6,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 96,4</t>
+          <t>-2,6; 101,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,72; 164,01</t>
+          <t>50,17; 161,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,85; 301,88</t>
+          <t>88,89; 288,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>65,11; 372,4</t>
+          <t>30,05; 150,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>3,87</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 9,08</t>
+          <t>2,66; 8,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 10,55</t>
+          <t>3,99; 10,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 9,63</t>
+          <t>3,49; 9,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 4,1</t>
+          <t>0,82; 6,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,13; 185,06</t>
+          <t>33,4; 185,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,33; 251,86</t>
+          <t>51,49; 240,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,4; 275,55</t>
+          <t>50,25; 249,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-55,57; 59,98</t>
+          <t>6,29; 121,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>6,78</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>114,58%</t>
+          <t>133,62%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,34</t>
+          <t>1,79; 6,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,21</t>
+          <t>3,78; 9,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,75</t>
+          <t>0,51; 5,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 8,83</t>
+          <t>4,51; 8,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,6; 151,88</t>
+          <t>27,37; 144,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,29; 161,85</t>
+          <t>43,63; 156,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 108,57</t>
+          <t>5,97; 101,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,5; 204,22</t>
+          <t>71,65; 211,88</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,54</t>
+          <t>2,06; 4,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,85</t>
+          <t>5,72; 8,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,64</t>
+          <t>3,99; 6,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,18</t>
+          <t>3,93; 6,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,16; 96,6</t>
+          <t>34,81; 97,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,72; 146,27</t>
+          <t>76,37; 141,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,26; 140,87</t>
+          <t>69,32; 141,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,71; 133,57</t>
+          <t>60,2; 119,47</t>
         </is>
       </c>
     </row>
